--- a/reports/Debug-snowbowl-20260106/For The Week Ending (Actual)_Visits.xlsx
+++ b/reports/Debug-snowbowl-20260106/For The Week Ending (Actual)_Visits.xlsx
@@ -34,13 +34,13 @@
     <t>Snowbowl Passes</t>
   </si>
   <si>
+    <t>Snowbowl Tickets</t>
+  </si>
+  <si>
+    <t>Snowbowl Uplift Tickets</t>
+  </si>
+  <si>
     <t>Snowbowl Comp Tickets</t>
-  </si>
-  <si>
-    <t>Snowbowl Uplift Tickets</t>
-  </si>
-  <si>
-    <t>Snowbowl Tickets</t>
   </si>
 </sst>
 </file>
@@ -445,10 +445,10 @@
         <v>1</v>
       </c>
       <c r="B3" s="2">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="C3" s="2">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>5</v>
@@ -459,13 +459,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="2">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="C4" s="2">
-        <v>1</v>
+        <v>1546</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -476,10 +476,10 @@
         <v>46027</v>
       </c>
       <c r="C5" s="2">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -487,10 +487,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="2">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="C6" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>5</v>
@@ -504,10 +504,10 @@
         <v>46027</v>
       </c>
       <c r="C7" s="2">
-        <v>378</v>
+        <v>32</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -515,7 +515,7 @@
         <v>1</v>
       </c>
       <c r="B8" s="2">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="C8" s="2">
         <v>3</v>
@@ -529,10 +529,10 @@
         <v>1</v>
       </c>
       <c r="B9" s="2">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="C9" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>5</v>
@@ -543,13 +543,13 @@
         <v>1</v>
       </c>
       <c r="B10" s="2">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="C10" s="2">
-        <v>241</v>
+        <v>550</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -557,13 +557,13 @@
         <v>1</v>
       </c>
       <c r="B11" s="2">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="C11" s="2">
-        <v>1</v>
+        <v>1826</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -574,7 +574,7 @@
         <v>46028</v>
       </c>
       <c r="C12" s="2">
-        <v>1546</v>
+        <v>279</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>8</v>
@@ -585,10 +585,10 @@
         <v>1</v>
       </c>
       <c r="B13" s="2">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="C13" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>5</v>
@@ -602,10 +602,10 @@
         <v>46028</v>
       </c>
       <c r="C14" s="2">
-        <v>472</v>
+        <v>241</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -616,7 +616,7 @@
         <v>46027</v>
       </c>
       <c r="C15" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>5</v>
@@ -627,10 +627,10 @@
         <v>1</v>
       </c>
       <c r="B16" s="2">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="C16" s="2">
-        <v>1</v>
+        <v>472</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>5</v>
@@ -644,7 +644,7 @@
         <v>46027</v>
       </c>
       <c r="C17" s="2">
-        <v>550</v>
+        <v>1</v>
       </c>
       <c r="D17" s="2" t="s">
         <v>5</v>
@@ -658,7 +658,7 @@
         <v>46027</v>
       </c>
       <c r="C18" s="2">
-        <v>1826</v>
+        <v>356</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>8</v>
@@ -669,13 +669,13 @@
         <v>1</v>
       </c>
       <c r="B19" s="2">
-        <v>46028</v>
+        <v>46027</v>
       </c>
       <c r="C19" s="2">
-        <v>280</v>
+        <v>1</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
